--- a/Document/Techincal/Features.xlsx
+++ b/Document/Techincal/Features.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Features" sheetId="1" r:id="rId1"/>
     <sheet name="Schema" sheetId="2" r:id="rId2"/>
     <sheet name="Tables" sheetId="3" r:id="rId3"/>
     <sheet name="API's" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="471">
   <si>
     <t>Feature / Page Name</t>
   </si>
@@ -168,6 +169,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -256,6 +265,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">2. </t>
     </r>
     <r>
@@ -293,6 +310,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">3. </t>
     </r>
     <r>
@@ -324,6 +349,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">4. </t>
     </r>
     <r>
@@ -394,6 +427,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">5. </t>
     </r>
     <r>
@@ -428,6 +469,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">6. </t>
     </r>
     <r>
@@ -459,6 +508,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">7. </t>
     </r>
     <r>
@@ -490,6 +547,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">8. </t>
     </r>
     <r>
@@ -521,6 +586,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">9. </t>
     </r>
     <r>
@@ -564,6 +637,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">10. </t>
     </r>
     <r>
@@ -613,6 +694,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">11. </t>
     </r>
     <r>
@@ -638,6 +727,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">12. </t>
     </r>
     <r>
@@ -666,6 +763,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">13. </t>
     </r>
     <r>
@@ -694,6 +799,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">14. </t>
     </r>
     <r>
@@ -713,6 +826,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">15. </t>
     </r>
     <r>
@@ -738,6 +859,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">16. </t>
     </r>
     <r>
@@ -781,6 +910,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">17. </t>
     </r>
     <r>
@@ -809,6 +946,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">18. </t>
     </r>
     <r>
@@ -843,6 +988,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">19. </t>
     </r>
     <r>
@@ -877,6 +1030,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">20. </t>
     </r>
     <r>
@@ -893,6 +1054,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">21. </t>
     </r>
     <r>
@@ -915,6 +1084,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">22. </t>
     </r>
     <r>
@@ -952,6 +1129,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">23. </t>
     </r>
     <r>
@@ -974,6 +1159,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">24. </t>
     </r>
     <r>
@@ -993,6 +1186,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">25. </t>
     </r>
     <r>
@@ -1030,6 +1231,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">26. </t>
     </r>
     <r>
@@ -1067,6 +1276,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">27. </t>
     </r>
     <r>
@@ -1092,6 +1309,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">28. </t>
     </r>
     <r>
@@ -1123,6 +1348,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">29. </t>
     </r>
     <r>
@@ -1148,6 +1381,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">30. </t>
     </r>
     <r>
@@ -1176,6 +1417,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">31. </t>
     </r>
     <r>
@@ -1204,6 +1453,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">32. </t>
     </r>
     <r>
@@ -1226,6 +1483,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">33. </t>
     </r>
     <r>
@@ -1251,6 +1516,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">34. </t>
     </r>
     <r>
@@ -1273,6 +1546,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">35. </t>
     </r>
     <r>
@@ -1802,6 +2083,122 @@
   </si>
   <si>
     <t>/admin/reports/sales</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">APIs </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in this exact order</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Brand</t>
+  </si>
+  <si>
+    <t>2. Category</t>
+  </si>
+  <si>
+    <t>3. Product</t>
+  </si>
+  <si>
+    <t>4. ProductVariant</t>
+  </si>
+  <si>
+    <t>public</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /api/brands</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /api/brands/{brandId}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /api/brands/{brandId} </t>
+  </si>
+  <si>
+    <t>/api/brands</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>/api/brands/{brandId}</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>/api/categories</t>
+  </si>
+  <si>
+    <t>/api/categories/{categoryId}</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>/api/products</t>
+  </si>
+  <si>
+    <t>/api/products/{productId}</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET    </t>
+  </si>
+  <si>
+    <t>/api/products?brandId=1&amp;categoryId=2</t>
+  </si>
+  <si>
+    <t>Get products by certain brand and categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET </t>
+  </si>
+  <si>
+    <t>/api/products?categoryId=2</t>
+  </si>
+  <si>
+    <t>/api/products?brandId=1</t>
+  </si>
+  <si>
+    <t>Product Variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /api/products/{productId}/variants</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /api/variants/{variantId}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /api/variants/{variantId}     </t>
+  </si>
+  <si>
+    <t>/api/products/{productId}/variants</t>
   </si>
 </sst>
 </file>
@@ -1825,6 +2222,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -1833,14 +2238,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -1999,12 +2396,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2217,12 +2620,77 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="20">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2296,21 +2764,6 @@
       <top/>
       <bottom style="thin">
         <color rgb="FFAAAAAA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2438,7 +2891,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2450,180 +2903,210 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2632,7 +3115,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3169,173 +3652,173 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="40.4285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="40.4259259259259" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="16384" width="40.4285714285714" customWidth="1"/>
+    <col min="1" max="16384" width="40.4259259259259" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" spans="1:3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="30" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="30" spans="1:3">
-      <c r="A2" s="23" t="s">
+    <row r="2" ht="28.8" spans="1:3">
+      <c r="A2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="45" spans="1:3">
-      <c r="A3" s="23" t="s">
+    <row r="3" ht="28.8" spans="1:3">
+      <c r="A3" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="31" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="45" spans="1:3">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="31" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="30" spans="1:3">
-      <c r="A5" s="23" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="31" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="60" spans="1:3">
-      <c r="A6" s="23" t="s">
+    <row r="6" ht="28.8" spans="1:3">
+      <c r="A6" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="31" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="60" spans="1:3">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="31" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="30" spans="1:3">
-      <c r="A8" s="23" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="31" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="45" spans="1:3">
-      <c r="A9" s="23" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="45" spans="1:3">
-      <c r="A10" s="23" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="45" spans="1:3">
-      <c r="A11" s="23" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="31" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" ht="45" spans="1:3">
-      <c r="A12" s="23" t="s">
+    <row r="12" ht="28.8" spans="1:3">
+      <c r="A12" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" ht="45" spans="1:3">
-      <c r="A13" s="23" t="s">
+    <row r="13" spans="1:3">
+      <c r="A13" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="31" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" ht="45" spans="1:3">
-      <c r="A14" s="23" t="s">
+    <row r="14" spans="1:3">
+      <c r="A14" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="31" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" ht="30" spans="1:3">
-      <c r="A15" s="23" t="s">
+    <row r="15" spans="1:3">
+      <c r="A15" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="31" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3372,15 +3855,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C387"/>
-  <sheetFormatPr defaultColWidth="18.7142857142857" defaultRowHeight="15" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="18.712962962963" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="68.1428571428571" customWidth="1"/>
-    <col min="2" max="3" width="18.4285714285714" customWidth="1"/>
-    <col min="4" max="16384" width="18.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="68.1388888888889" customWidth="1"/>
+    <col min="2" max="3" width="18.4259259259259" customWidth="1"/>
+    <col min="4" max="16384" width="18.712962962963" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" spans="1:1">
-      <c r="A1" s="19" t="s">
+    <row r="1" ht="23.4" spans="1:1">
+      <c r="A1" s="29" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3390,106 +3873,106 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="31" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="31" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="31" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="31" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="31" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="31" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="31" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="31" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" ht="23.25" spans="1:1">
-      <c r="A14" s="19" t="s">
+    <row r="14" ht="23.4" spans="1:1">
+      <c r="A14" s="29" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3499,39 +3982,39 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="31" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" ht="30" spans="1:2">
-      <c r="A20" s="21" t="s">
+    <row r="20" ht="28.8" spans="1:2">
+      <c r="A20" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="31" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="31" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="24" ht="23.25" spans="1:1">
-      <c r="A24" s="19" t="s">
+    <row r="24" ht="23.4" spans="1:1">
+      <c r="A24" s="29" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3541,37 +4024,37 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="21"/>
+      <c r="B29" s="31"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="31" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="31" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="34" ht="23.25" spans="1:1">
-      <c r="A34" s="19" t="s">
+    <row r="34" ht="23.4" spans="1:1">
+      <c r="A34" s="29" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3581,147 +4064,147 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B39" s="21"/>
+      <c r="B39" s="31"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="31" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="31" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="31" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="31" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="31" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="31" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="31" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="31" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="B48" s="21" t="s">
+      <c r="B48" s="31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="51" ht="23.25" spans="1:1">
-      <c r="A51" s="19" t="s">
+    <row r="51" ht="23.4" spans="1:1">
+      <c r="A51" s="29" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="20" t="s">
+      <c r="A53" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B54" s="21"/>
+      <c r="B54" s="31"/>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="21" t="s">
+      <c r="A55" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B55" s="21"/>
+      <c r="B55" s="31"/>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="21" t="s">
+      <c r="A56" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="31" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="21" t="s">
+      <c r="A57" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="31" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="21" t="s">
+      <c r="A58" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="61" ht="31.5" spans="1:1">
-      <c r="A61" s="22" t="s">
+    <row r="61" ht="31.2" spans="1:1">
+      <c r="A61" s="32" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="63" ht="23.25" spans="1:1">
-      <c r="A63" s="19" t="s">
+    <row r="63" ht="23.4" spans="1:1">
+      <c r="A63" s="29" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3731,57 +4214,57 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="20" t="s">
+      <c r="A67" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B67" s="20" t="s">
+      <c r="B67" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B68" s="21"/>
+      <c r="B68" s="31"/>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="21" t="s">
+      <c r="A69" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B69" s="21" t="s">
+      <c r="B69" s="31" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="21" t="s">
+      <c r="A70" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="B70" s="21" t="s">
+      <c r="B70" s="31" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="21" t="s">
+      <c r="A71" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B71" s="21"/>
+      <c r="B71" s="31"/>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="21" t="s">
+      <c r="A72" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="31" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="21" t="s">
+      <c r="A73" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B73" s="21"/>
-    </row>
-    <row r="76" ht="23.25" spans="1:1">
-      <c r="A76" s="19" t="s">
+      <c r="B73" s="31"/>
+    </row>
+    <row r="76" ht="23.4" spans="1:1">
+      <c r="A76" s="29" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3791,37 +4274,37 @@
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="20" t="s">
+      <c r="A80" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B80" s="20" t="s">
+      <c r="B80" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="21" t="s">
+      <c r="A81" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B81" s="21"/>
+      <c r="B81" s="31"/>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="21" t="s">
+      <c r="A82" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="B82" s="21" t="s">
+      <c r="B82" s="31" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="21" t="s">
+      <c r="A83" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="B83" s="21" t="s">
+      <c r="B83" s="31" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="86" ht="23.25" spans="1:1">
-      <c r="A86" s="19" t="s">
+    <row r="86" ht="23.4" spans="1:1">
+      <c r="A86" s="29" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3831,56 +4314,56 @@
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="20" t="s">
+      <c r="A90" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B90" s="20" t="s">
+      <c r="B90" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="21" t="s">
+      <c r="A91" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B91" s="21"/>
+      <c r="B91" s="31"/>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="21" t="s">
+      <c r="A92" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B92" s="21" t="s">
+      <c r="B92" s="31" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="21" t="s">
+      <c r="A93" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B93" s="21"/>
+      <c r="B93" s="31"/>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="21" t="s">
+      <c r="A94" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B94" s="21" t="s">
+      <c r="B94" s="31" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="21" t="s">
+      <c r="A95" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="B95" s="21" t="s">
+      <c r="B95" s="31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="98" ht="31.5" spans="1:1">
-      <c r="A98" s="22" t="s">
+    <row r="98" ht="31.2" spans="1:1">
+      <c r="A98" s="32" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="100" ht="23.25" spans="1:1">
-      <c r="A100" s="19" t="s">
+    <row r="100" ht="23.4" spans="1:1">
+      <c r="A100" s="29" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3890,83 +4373,83 @@
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="20" t="s">
+      <c r="A104" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B104" s="20" t="s">
+      <c r="B104" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="21" t="s">
+      <c r="A105" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B105" s="21"/>
+      <c r="B105" s="31"/>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="21" t="s">
+      <c r="A106" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="B106" s="21" t="s">
+      <c r="B106" s="31" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="21" t="s">
+      <c r="A107" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B107" s="21" t="s">
+      <c r="B107" s="31" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="21" t="s">
+      <c r="A108" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B108" s="21" t="s">
+      <c r="B108" s="31" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="21" t="s">
+      <c r="A109" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B109" s="21" t="s">
+      <c r="B109" s="31" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="21" t="s">
+      <c r="A110" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="B110" s="21" t="s">
+      <c r="B110" s="31" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="21" t="s">
+      <c r="A111" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="B111" s="21" t="s">
+      <c r="B111" s="31" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="21" t="s">
+      <c r="A112" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="B112" s="21" t="s">
+      <c r="B112" s="31" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="21" t="s">
+      <c r="A113" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B113" s="21"/>
-    </row>
-    <row r="116" ht="23.25" spans="1:1">
-      <c r="A116" s="19" t="s">
+      <c r="B113" s="31"/>
+    </row>
+    <row r="116" ht="23.4" spans="1:1">
+      <c r="A116" s="29" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3976,110 +4459,110 @@
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="20" t="s">
+      <c r="A120" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B120" s="20" t="s">
+      <c r="B120" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="21" t="s">
+      <c r="A121" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B121" s="21"/>
+      <c r="B121" s="31"/>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="21" t="s">
+      <c r="A122" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="B122" s="21" t="s">
+      <c r="B122" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="21" t="s">
+      <c r="A123" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="B123" s="21" t="s">
+      <c r="B123" s="31" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="124" ht="30" spans="1:2">
-      <c r="A124" s="21" t="s">
+    <row r="124" ht="28.8" spans="1:2">
+      <c r="A124" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="B124" s="21" t="s">
+      <c r="B124" s="31" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="21" t="s">
+      <c r="A125" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="B125" s="21" t="s">
+      <c r="B125" s="31" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="21" t="s">
+      <c r="A126" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="B126" s="21" t="s">
+      <c r="B126" s="31" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="21" t="s">
+      <c r="A127" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="B127" s="21" t="s">
+      <c r="B127" s="31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="130" ht="23.25" spans="1:1">
-      <c r="A130" s="19" t="s">
+    <row r="130" ht="23.4" spans="1:1">
+      <c r="A130" s="29" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="20" t="s">
+      <c r="A132" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B132" s="20" t="s">
+      <c r="B132" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="21" t="s">
+      <c r="A133" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B133" s="21"/>
+      <c r="B133" s="31"/>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="21" t="s">
+      <c r="A134" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="B134" s="21"/>
+      <c r="B134" s="31"/>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="21" t="s">
+      <c r="A135" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="B135" s="21" t="s">
+      <c r="B135" s="31" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="21" t="s">
+      <c r="A136" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="B136" s="21" t="s">
+      <c r="B136" s="31" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="139" ht="23.25" spans="1:1">
-      <c r="A139" s="19" t="s">
+    <row r="139" ht="23.4" spans="1:1">
+      <c r="A139" s="29" t="s">
         <v>154</v>
       </c>
     </row>
@@ -4089,37 +4572,37 @@
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="20" t="s">
+      <c r="A143" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B143" s="20" t="s">
+      <c r="B143" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="21" t="s">
+      <c r="A144" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B144" s="21"/>
+      <c r="B144" s="31"/>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="21" t="s">
+      <c r="A145" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B145" s="21" t="s">
+      <c r="B145" s="31" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="21" t="s">
+      <c r="A146" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="B146" s="21" t="s">
+      <c r="B146" s="31" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="149" ht="23.25" spans="1:1">
-      <c r="A149" s="19" t="s">
+    <row r="149" ht="23.4" spans="1:1">
+      <c r="A149" s="29" t="s">
         <v>159</v>
       </c>
     </row>
@@ -4129,41 +4612,41 @@
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="20" t="s">
+      <c r="A153" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B153" s="20" t="s">
+      <c r="B153" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="21" t="s">
+      <c r="A154" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B154" s="21"/>
+      <c r="B154" s="31"/>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="21" t="s">
+      <c r="A155" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="B155" s="21"/>
+      <c r="B155" s="31"/>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="21" t="s">
+      <c r="A156" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="B156" s="21"/>
+      <c r="B156" s="31"/>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="21" t="s">
+      <c r="A157" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="B157" s="21" t="s">
+      <c r="B157" s="31" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="160" ht="23.25" spans="1:1">
-      <c r="A160" s="19" t="s">
+    <row r="160" ht="23.4" spans="1:1">
+      <c r="A160" s="29" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4173,1006 +4656,1006 @@
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="20" t="s">
+      <c r="A164" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B164" s="20" t="s">
+      <c r="B164" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="21" t="s">
+      <c r="A165" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B165" s="21"/>
+      <c r="B165" s="31"/>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="21" t="s">
+      <c r="A166" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="B166" s="21"/>
+      <c r="B166" s="31"/>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="21" t="s">
+      <c r="A167" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="B167" s="21"/>
-    </row>
-    <row r="170" ht="23.25" spans="1:1">
-      <c r="A170" s="19" t="s">
+      <c r="B167" s="31"/>
+    </row>
+    <row r="170" ht="23.4" spans="1:1">
+      <c r="A170" s="29" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="20" t="s">
+      <c r="A172" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B172" s="20" t="s">
+      <c r="B172" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="21" t="s">
+      <c r="A173" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B173" s="21"/>
+      <c r="B173" s="31"/>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="21" t="s">
+      <c r="A174" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="B174" s="21"/>
+      <c r="B174" s="31"/>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="21" t="s">
+      <c r="A175" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="B175" s="21" t="s">
+      <c r="B175" s="31" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="178" ht="31.5" spans="1:1">
-      <c r="A178" s="22" t="s">
+    <row r="178" ht="31.2" spans="1:1">
+      <c r="A178" s="32" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="180" ht="23.25" spans="1:1">
-      <c r="A180" s="19" t="s">
+    <row r="180" ht="23.4" spans="1:1">
+      <c r="A180" s="29" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="20" t="s">
+      <c r="A182" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B182" s="20" t="s">
+      <c r="B182" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="21" t="s">
+      <c r="A183" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B183" s="21"/>
+      <c r="B183" s="31"/>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="21" t="s">
+      <c r="A184" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="B184" s="21"/>
+      <c r="B184" s="31"/>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="21" t="s">
+      <c r="A185" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="B185" s="21" t="s">
+      <c r="B185" s="31" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="21" t="s">
+      <c r="A186" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="B186" s="21" t="s">
+      <c r="B186" s="31" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="21" t="s">
+      <c r="A187" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="B187" s="21" t="s">
+      <c r="B187" s="31" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="21" t="s">
+      <c r="A188" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="B188" s="21" t="s">
+      <c r="B188" s="31" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="191" ht="23.25" spans="1:1">
-      <c r="A191" s="19" t="s">
+    <row r="191" ht="23.4" spans="1:1">
+      <c r="A191" s="29" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="20" t="s">
+      <c r="A193" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B193" s="20" t="s">
+      <c r="B193" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="21" t="s">
+      <c r="A194" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B194" s="21"/>
+      <c r="B194" s="31"/>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="21" t="s">
+      <c r="A195" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="B195" s="21"/>
+      <c r="B195" s="31"/>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="21" t="s">
+      <c r="A196" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="B196" s="21"/>
+      <c r="B196" s="31"/>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="21" t="s">
+      <c r="A197" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="B197" s="21"/>
+      <c r="B197" s="31"/>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="21" t="s">
+      <c r="A198" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="B198" s="21"/>
-    </row>
-    <row r="201" ht="23.25" spans="1:1">
-      <c r="A201" s="19" t="s">
+      <c r="B198" s="31"/>
+    </row>
+    <row r="201" ht="23.4" spans="1:1">
+      <c r="A201" s="29" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="20" t="s">
+      <c r="A203" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B203" s="20" t="s">
+      <c r="B203" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="21" t="s">
+      <c r="A204" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B204" s="21"/>
+      <c r="B204" s="31"/>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="21" t="s">
+      <c r="A205" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="B205" s="21"/>
+      <c r="B205" s="31"/>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="21" t="s">
+      <c r="A206" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="B206" s="21" t="s">
+      <c r="B206" s="31" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="21" t="s">
+      <c r="A207" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="B207" s="21" t="s">
+      <c r="B207" s="31" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="21" t="s">
+      <c r="A208" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="B208" s="21" t="s">
+      <c r="B208" s="31" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="211" ht="23.25" spans="1:1">
-      <c r="A211" s="19" t="s">
+    <row r="211" ht="23.4" spans="1:1">
+      <c r="A211" s="29" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="20" t="s">
+      <c r="A213" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B213" s="20" t="s">
+      <c r="B213" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="21" t="s">
+      <c r="A214" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B214" s="21"/>
+      <c r="B214" s="31"/>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="21" t="s">
+      <c r="A215" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="B215" s="21"/>
+      <c r="B215" s="31"/>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="21" t="s">
+      <c r="A216" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="B216" s="21" t="s">
+      <c r="B216" s="31" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="21" t="s">
+      <c r="A217" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="B217" s="21"/>
+      <c r="B217" s="31"/>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="21" t="s">
+      <c r="A218" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="B218" s="21" t="s">
+      <c r="B218" s="31" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="21" t="s">
+      <c r="A219" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B219" s="21"/>
-    </row>
-    <row r="222" ht="31.5" spans="1:1">
-      <c r="A222" s="22" t="s">
+      <c r="B219" s="31"/>
+    </row>
+    <row r="222" ht="31.2" spans="1:1">
+      <c r="A222" s="32" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="224" ht="23.25" spans="1:1">
-      <c r="A224" s="19" t="s">
+    <row r="224" ht="23.4" spans="1:1">
+      <c r="A224" s="29" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="20" t="s">
+      <c r="A226" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B226" s="20" t="s">
+      <c r="B226" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="21" t="s">
+      <c r="A227" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B227" s="21"/>
+      <c r="B227" s="31"/>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="21" t="s">
+      <c r="A228" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B228" s="21"/>
+      <c r="B228" s="31"/>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="21" t="s">
+      <c r="A229" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B229" s="21"/>
-    </row>
-    <row r="232" ht="23.25" spans="1:1">
-      <c r="A232" s="19" t="s">
+      <c r="B229" s="31"/>
+    </row>
+    <row r="232" ht="23.4" spans="1:1">
+      <c r="A232" s="29" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="234" spans="1:2">
-      <c r="A234" s="20" t="s">
+      <c r="A234" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B234" s="20" t="s">
+      <c r="B234" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="235" spans="1:2">
-      <c r="A235" s="21" t="s">
+      <c r="A235" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B235" s="21"/>
+      <c r="B235" s="31"/>
     </row>
     <row r="236" spans="1:2">
-      <c r="A236" s="21" t="s">
+      <c r="A236" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="B236" s="21"/>
+      <c r="B236" s="31"/>
     </row>
     <row r="237" spans="1:2">
-      <c r="A237" s="21" t="s">
+      <c r="A237" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="B237" s="21"/>
+      <c r="B237" s="31"/>
     </row>
     <row r="238" spans="1:2">
-      <c r="A238" s="21" t="s">
+      <c r="A238" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="B238" s="21"/>
+      <c r="B238" s="31"/>
     </row>
     <row r="239" spans="1:2">
-      <c r="A239" s="21" t="s">
+      <c r="A239" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="B239" s="21"/>
-    </row>
-    <row r="242" ht="23.25" spans="1:1">
-      <c r="A242" s="19" t="s">
+      <c r="B239" s="31"/>
+    </row>
+    <row r="242" ht="23.4" spans="1:1">
+      <c r="A242" s="29" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="244" spans="1:2">
-      <c r="A244" s="20" t="s">
+      <c r="A244" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B244" s="20" t="s">
+      <c r="B244" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="245" spans="1:2">
-      <c r="A245" s="21" t="s">
+      <c r="A245" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B245" s="21"/>
+      <c r="B245" s="31"/>
     </row>
     <row r="246" spans="1:2">
-      <c r="A246" s="21" t="s">
+      <c r="A246" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="B246" s="21"/>
+      <c r="B246" s="31"/>
     </row>
     <row r="247" spans="1:2">
-      <c r="A247" s="21" t="s">
+      <c r="A247" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="B247" s="21" t="s">
+      <c r="B247" s="31" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="248" spans="1:2">
-      <c r="A248" s="21" t="s">
+      <c r="A248" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="B248" s="21"/>
+      <c r="B248" s="31"/>
     </row>
     <row r="249" spans="1:2">
-      <c r="A249" s="21" t="s">
+      <c r="A249" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="B249" s="21" t="s">
+      <c r="B249" s="31" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="250" spans="1:2">
-      <c r="A250" s="21" t="s">
+      <c r="A250" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="B250" s="21" t="s">
+      <c r="B250" s="31" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="251" spans="1:2">
-      <c r="A251" s="21" t="s">
+      <c r="A251" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B251" s="21"/>
-    </row>
-    <row r="254" ht="23.25" spans="1:1">
-      <c r="A254" s="19" t="s">
+      <c r="B251" s="31"/>
+    </row>
+    <row r="254" ht="23.4" spans="1:1">
+      <c r="A254" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="256" spans="1:2">
-      <c r="A256" s="20" t="s">
+      <c r="A256" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B256" s="20" t="s">
+      <c r="B256" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="257" spans="1:2">
-      <c r="A257" s="21" t="s">
+      <c r="A257" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B257" s="21"/>
+      <c r="B257" s="31"/>
     </row>
     <row r="258" spans="1:2">
-      <c r="A258" s="21" t="s">
+      <c r="A258" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B258" s="21"/>
+      <c r="B258" s="31"/>
     </row>
     <row r="259" spans="1:2">
-      <c r="A259" s="21" t="s">
+      <c r="A259" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="B259" s="21"/>
+      <c r="B259" s="31"/>
     </row>
     <row r="260" spans="1:2">
-      <c r="A260" s="21" t="s">
+      <c r="A260" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="B260" s="21"/>
+      <c r="B260" s="31"/>
     </row>
     <row r="261" spans="1:2">
-      <c r="A261" s="21" t="s">
+      <c r="A261" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="B261" s="21"/>
-    </row>
-    <row r="264" ht="23.25" spans="1:1">
-      <c r="A264" s="19" t="s">
+      <c r="B261" s="31"/>
+    </row>
+    <row r="264" ht="23.4" spans="1:1">
+      <c r="A264" s="29" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="266" spans="1:2">
-      <c r="A266" s="20" t="s">
+      <c r="A266" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B266" s="20" t="s">
+      <c r="B266" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="267" spans="1:2">
-      <c r="A267" s="21" t="s">
+      <c r="A267" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B267" s="21"/>
+      <c r="B267" s="31"/>
     </row>
     <row r="268" spans="1:2">
-      <c r="A268" s="21" t="s">
+      <c r="A268" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="B268" s="21"/>
+      <c r="B268" s="31"/>
     </row>
     <row r="269" spans="1:2">
-      <c r="A269" s="21" t="s">
+      <c r="A269" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B269" s="21"/>
+      <c r="B269" s="31"/>
     </row>
     <row r="270" spans="1:2">
-      <c r="A270" s="21" t="s">
+      <c r="A270" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="B270" s="21"/>
-    </row>
-    <row r="273" ht="23.25" spans="1:1">
-      <c r="A273" s="19" t="s">
+      <c r="B270" s="31"/>
+    </row>
+    <row r="273" ht="23.4" spans="1:1">
+      <c r="A273" s="29" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="275" spans="1:2">
-      <c r="A275" s="20" t="s">
+      <c r="A275" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B275" s="20" t="s">
+      <c r="B275" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="276" spans="1:2">
-      <c r="A276" s="21" t="s">
+      <c r="A276" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B276" s="21"/>
+      <c r="B276" s="31"/>
     </row>
     <row r="277" spans="1:2">
-      <c r="A277" s="21" t="s">
+      <c r="A277" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B277" s="21"/>
+      <c r="B277" s="31"/>
     </row>
     <row r="278" spans="1:2">
-      <c r="A278" s="21" t="s">
+      <c r="A278" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B278" s="21" t="s">
+      <c r="B278" s="31" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="279" spans="1:2">
-      <c r="A279" s="21" t="s">
+      <c r="A279" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="B279" s="21"/>
+      <c r="B279" s="31"/>
     </row>
     <row r="280" spans="1:2">
-      <c r="A280" s="21" t="s">
+      <c r="A280" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="B280" s="21"/>
+      <c r="B280" s="31"/>
     </row>
     <row r="281" spans="1:2">
-      <c r="A281" s="21" t="s">
+      <c r="A281" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B281" s="21"/>
+      <c r="B281" s="31"/>
     </row>
     <row r="282" spans="1:2">
-      <c r="A282" s="21" t="s">
+      <c r="A282" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="B282" s="21" t="s">
+      <c r="B282" s="31" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="285" ht="31.5" spans="1:1">
-      <c r="A285" s="22" t="s">
+    <row r="285" ht="31.2" spans="1:1">
+      <c r="A285" s="32" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="287" ht="23.25" spans="1:1">
-      <c r="A287" s="19" t="s">
+    <row r="287" ht="23.4" spans="1:1">
+      <c r="A287" s="29" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="289" spans="1:2">
-      <c r="A289" s="20" t="s">
+      <c r="A289" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B289" s="20" t="s">
+      <c r="B289" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="21" t="s">
+      <c r="A290" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B290" s="21"/>
+      <c r="B290" s="31"/>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="21" t="s">
+      <c r="A291" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="B291" s="21" t="s">
+      <c r="B291" s="31" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="292" spans="1:2">
-      <c r="A292" s="21" t="s">
+      <c r="A292" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="B292" s="21" t="s">
+      <c r="B292" s="31" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="293" spans="1:2">
-      <c r="A293" s="21" t="s">
+      <c r="A293" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="B293" s="21"/>
+      <c r="B293" s="31"/>
     </row>
     <row r="294" spans="1:2">
-      <c r="A294" s="21" t="s">
+      <c r="A294" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="B294" s="21"/>
+      <c r="B294" s="31"/>
     </row>
     <row r="295" spans="1:2">
-      <c r="A295" s="21" t="s">
+      <c r="A295" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="B295" s="21"/>
-    </row>
-    <row r="298" ht="23.25" spans="1:1">
-      <c r="A298" s="19" t="s">
+      <c r="B295" s="31"/>
+    </row>
+    <row r="298" ht="23.4" spans="1:1">
+      <c r="A298" s="29" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="300" spans="1:2">
-      <c r="A300" s="20" t="s">
+      <c r="A300" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B300" s="20" t="s">
+      <c r="B300" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="301" spans="1:2">
-      <c r="A301" s="21" t="s">
+      <c r="A301" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B301" s="21"/>
+      <c r="B301" s="31"/>
     </row>
     <row r="302" spans="1:2">
-      <c r="A302" s="21" t="s">
+      <c r="A302" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="B302" s="21"/>
+      <c r="B302" s="31"/>
     </row>
     <row r="303" spans="1:2">
-      <c r="A303" s="21" t="s">
+      <c r="A303" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="B303" s="21"/>
+      <c r="B303" s="31"/>
     </row>
     <row r="304" spans="1:2">
-      <c r="A304" s="21" t="s">
+      <c r="A304" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="B304" s="21"/>
-    </row>
-    <row r="307" ht="23.25" spans="1:1">
-      <c r="A307" s="19" t="s">
+      <c r="B304" s="31"/>
+    </row>
+    <row r="307" ht="23.4" spans="1:1">
+      <c r="A307" s="29" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="309" spans="1:2">
-      <c r="A309" s="20" t="s">
+      <c r="A309" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B309" s="20" t="s">
+      <c r="B309" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="310" spans="1:2">
-      <c r="A310" s="21" t="s">
+      <c r="A310" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B310" s="21"/>
+      <c r="B310" s="31"/>
     </row>
     <row r="311" spans="1:2">
-      <c r="A311" s="21" t="s">
+      <c r="A311" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B311" s="21"/>
-    </row>
-    <row r="312" ht="30" spans="1:2">
-      <c r="A312" s="21" t="s">
+      <c r="B311" s="31"/>
+    </row>
+    <row r="312" ht="28.8" spans="1:2">
+      <c r="A312" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="B312" s="21" t="s">
+      <c r="B312" s="31" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="313" spans="1:2">
-      <c r="A313" s="21" t="s">
+      <c r="A313" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="B313" s="21"/>
+      <c r="B313" s="31"/>
     </row>
     <row r="314" spans="1:2">
-      <c r="A314" s="21" t="s">
+      <c r="A314" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="B314" s="21"/>
+      <c r="B314" s="31"/>
     </row>
     <row r="315" spans="1:2">
-      <c r="A315" s="21" t="s">
+      <c r="A315" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="B315" s="21"/>
-    </row>
-    <row r="318" ht="23.25" spans="1:1">
-      <c r="A318" s="19" t="s">
+      <c r="B315" s="31"/>
+    </row>
+    <row r="318" ht="23.4" spans="1:1">
+      <c r="A318" s="29" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="320" spans="1:2">
-      <c r="A320" s="20" t="s">
+      <c r="A320" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B320" s="20" t="s">
+      <c r="B320" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="321" spans="1:2">
-      <c r="A321" s="21" t="s">
+      <c r="A321" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B321" s="21"/>
+      <c r="B321" s="31"/>
     </row>
     <row r="322" spans="1:2">
-      <c r="A322" s="21" t="s">
+      <c r="A322" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="B322" s="21"/>
+      <c r="B322" s="31"/>
     </row>
     <row r="323" spans="1:2">
-      <c r="A323" s="21" t="s">
+      <c r="A323" s="31" t="s">
         <v>243</v>
       </c>
-      <c r="B323" s="21"/>
+      <c r="B323" s="31"/>
     </row>
     <row r="324" spans="1:2">
-      <c r="A324" s="21" t="s">
+      <c r="A324" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="B324" s="21"/>
-    </row>
-    <row r="327" ht="31.5" spans="1:1">
-      <c r="A327" s="22" t="s">
+      <c r="B324" s="31"/>
+    </row>
+    <row r="327" ht="31.2" spans="1:1">
+      <c r="A327" s="32" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="329" ht="23.25" spans="1:1">
-      <c r="A329" s="19" t="s">
+    <row r="329" ht="23.4" spans="1:1">
+      <c r="A329" s="29" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="331" spans="1:2">
-      <c r="A331" s="20" t="s">
+      <c r="A331" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B331" s="20" t="s">
+      <c r="B331" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="332" spans="1:2">
-      <c r="A332" s="21" t="s">
+      <c r="A332" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B332" s="21"/>
+      <c r="B332" s="31"/>
     </row>
     <row r="333" spans="1:2">
-      <c r="A333" s="21" t="s">
+      <c r="A333" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="B333" s="21"/>
+      <c r="B333" s="31"/>
     </row>
     <row r="334" spans="1:2">
-      <c r="A334" s="21" t="s">
+      <c r="A334" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="B334" s="21"/>
+      <c r="B334" s="31"/>
     </row>
     <row r="335" spans="1:2">
-      <c r="A335" s="21" t="s">
+      <c r="A335" s="31" t="s">
         <v>248</v>
       </c>
-      <c r="B335" s="21" t="s">
+      <c r="B335" s="31" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="21" t="s">
+      <c r="A336" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="B336" s="21"/>
+      <c r="B336" s="31"/>
     </row>
     <row r="337" spans="1:2">
-      <c r="A337" s="21" t="s">
+      <c r="A337" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B337" s="21"/>
-    </row>
-    <row r="340" ht="23.25" spans="1:1">
-      <c r="A340" s="19" t="s">
+      <c r="B337" s="31"/>
+    </row>
+    <row r="340" ht="23.4" spans="1:1">
+      <c r="A340" s="29" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="342" spans="1:2">
-      <c r="A342" s="20" t="s">
+      <c r="A342" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B342" s="20" t="s">
+      <c r="B342" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="343" spans="1:2">
-      <c r="A343" s="21" t="s">
+      <c r="A343" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B343" s="21"/>
+      <c r="B343" s="31"/>
     </row>
     <row r="344" spans="1:2">
-      <c r="A344" s="21" t="s">
+      <c r="A344" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="B344" s="21"/>
+      <c r="B344" s="31"/>
     </row>
     <row r="345" spans="1:2">
-      <c r="A345" s="21" t="s">
+      <c r="A345" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="B345" s="21"/>
+      <c r="B345" s="31"/>
     </row>
     <row r="346" spans="1:2">
-      <c r="A346" s="21" t="s">
+      <c r="A346" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="B346" s="21"/>
+      <c r="B346" s="31"/>
     </row>
     <row r="347" spans="1:2">
-      <c r="A347" s="21" t="s">
+      <c r="A347" s="31" t="s">
         <v>254</v>
       </c>
-      <c r="B347" s="21"/>
+      <c r="B347" s="31"/>
     </row>
     <row r="348" spans="1:2">
-      <c r="A348" s="21" t="s">
+      <c r="A348" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="B348" s="21"/>
-    </row>
-    <row r="351" ht="23.25" spans="1:1">
-      <c r="A351" s="19" t="s">
+      <c r="B348" s="31"/>
+    </row>
+    <row r="351" ht="23.4" spans="1:1">
+      <c r="A351" s="29" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="353" spans="1:2">
-      <c r="A353" s="20" t="s">
+      <c r="A353" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B353" s="20" t="s">
+      <c r="B353" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="354" spans="1:2">
-      <c r="A354" s="21" t="s">
+      <c r="A354" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B354" s="21"/>
+      <c r="B354" s="31"/>
     </row>
     <row r="355" spans="1:2">
-      <c r="A355" s="21" t="s">
+      <c r="A355" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="B355" s="21"/>
+      <c r="B355" s="31"/>
     </row>
     <row r="356" spans="1:2">
-      <c r="A356" s="21" t="s">
+      <c r="A356" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="B356" s="21"/>
+      <c r="B356" s="31"/>
     </row>
     <row r="357" spans="1:2">
-      <c r="A357" s="21" t="s">
+      <c r="A357" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="B357" s="21"/>
-    </row>
-    <row r="360" ht="23.25" spans="1:1">
-      <c r="A360" s="19" t="s">
+      <c r="B357" s="31"/>
+    </row>
+    <row r="360" ht="23.4" spans="1:1">
+      <c r="A360" s="29" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="362" spans="1:2">
-      <c r="A362" s="20" t="s">
+      <c r="A362" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B362" s="20" t="s">
+      <c r="B362" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="363" spans="1:2">
-      <c r="A363" s="21" t="s">
+      <c r="A363" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B363" s="21"/>
+      <c r="B363" s="31"/>
     </row>
     <row r="364" spans="1:2">
-      <c r="A364" s="21" t="s">
+      <c r="A364" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="B364" s="21" t="s">
+      <c r="B364" s="31" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="21" t="s">
+      <c r="A365" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="B365" s="21" t="s">
+      <c r="B365" s="31" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="21" t="s">
+      <c r="A366" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="B366" s="21"/>
-    </row>
-    <row r="369" ht="31.5" spans="1:1">
-      <c r="A369" s="22" t="s">
+      <c r="B366" s="31"/>
+    </row>
+    <row r="369" ht="31.2" spans="1:1">
+      <c r="A369" s="32" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="371" ht="23.25" spans="1:1">
-      <c r="A371" s="19" t="s">
+    <row r="371" ht="23.4" spans="1:1">
+      <c r="A371" s="29" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="20" t="s">
+      <c r="A373" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B373" s="20" t="s">
+      <c r="B373" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="21" t="s">
+      <c r="A374" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B374" s="21"/>
+      <c r="B374" s="31"/>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="21" t="s">
+      <c r="A375" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="B375" s="21" t="s">
+      <c r="B375" s="31" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="21" t="s">
+      <c r="A376" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="B376" s="21">
+      <c r="B376" s="31">
         <v>18</v>
       </c>
     </row>
     <row r="377" spans="1:2">
-      <c r="A377" s="21" t="s">
+      <c r="A377" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B377" s="21"/>
-    </row>
-    <row r="380" ht="23.25" spans="1:1">
-      <c r="A380" s="19" t="s">
+      <c r="B377" s="31"/>
+    </row>
+    <row r="380" ht="23.4" spans="1:1">
+      <c r="A380" s="29" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="20" t="s">
+      <c r="A382" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B382" s="20" t="s">
+      <c r="B382" s="30" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="21" t="s">
+      <c r="A383" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B383" s="21"/>
+      <c r="B383" s="31"/>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="21" t="s">
+      <c r="A384" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="B384" s="21"/>
+      <c r="B384" s="31"/>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="21" t="s">
+      <c r="A385" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="B385" s="21" t="s">
+      <c r="B385" s="31" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="21" t="s">
+      <c r="A386" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="B386" s="21"/>
+      <c r="B386" s="31"/>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="21" t="s">
+      <c r="A387" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B387" s="21" t="s">
+      <c r="B387" s="31" t="s">
         <v>268</v>
       </c>
     </row>
@@ -5186,513 +5669,513 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S12"/>
-  <sheetFormatPr defaultColWidth="40.7142857142857" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="40.712962962963" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.42857142857143" customWidth="1"/>
-    <col min="2" max="2" width="21.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="38.1428571428571" customWidth="1"/>
+    <col min="1" max="1" width="8.42592592592593" customWidth="1"/>
+    <col min="2" max="2" width="21.712962962963" customWidth="1"/>
+    <col min="3" max="3" width="38.1388888888889" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="37.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="37.4259259259259" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="22.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="22.712962962963" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="21.1428571428571" customWidth="1"/>
-    <col min="10" max="10" width="13.4285714285714" customWidth="1"/>
-    <col min="11" max="11" width="21.7142857142857" customWidth="1"/>
-    <col min="12" max="12" width="14.1428571428571" customWidth="1"/>
-    <col min="13" max="13" width="18.8571428571429" customWidth="1"/>
-    <col min="14" max="14" width="14.7142857142857" customWidth="1"/>
-    <col min="15" max="15" width="22.4285714285714" customWidth="1"/>
-    <col min="16" max="16" width="16.5714285714286" customWidth="1"/>
-    <col min="17" max="17" width="18.7142857142857" customWidth="1"/>
-    <col min="18" max="18" width="14.8571428571429" customWidth="1"/>
-    <col min="19" max="19" width="27.4285714285714" customWidth="1"/>
-    <col min="20" max="16384" width="40.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="21.1388888888889" customWidth="1"/>
+    <col min="10" max="10" width="13.4259259259259" customWidth="1"/>
+    <col min="11" max="11" width="21.712962962963" customWidth="1"/>
+    <col min="12" max="12" width="14.1388888888889" customWidth="1"/>
+    <col min="13" max="13" width="18.8611111111111" customWidth="1"/>
+    <col min="14" max="14" width="14.712962962963" customWidth="1"/>
+    <col min="15" max="15" width="22.4259259259259" customWidth="1"/>
+    <col min="16" max="16" width="16.5740740740741" customWidth="1"/>
+    <col min="17" max="17" width="18.712962962963" customWidth="1"/>
+    <col min="18" max="18" width="14.8611111111111" customWidth="1"/>
+    <col min="19" max="19" width="27.4259259259259" customWidth="1"/>
+    <col min="20" max="16384" width="40.712962962963" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="24" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14" t="s">
+      <c r="C1" s="24"/>
+      <c r="D1" s="24" t="s">
         <v>271</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14" t="s">
+      <c r="E1" s="24"/>
+      <c r="F1" s="24" t="s">
         <v>272</v>
       </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14" t="s">
+      <c r="G1" s="24"/>
+      <c r="H1" s="24" t="s">
         <v>273</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14" t="s">
+      <c r="I1" s="24"/>
+      <c r="J1" s="24" t="s">
         <v>274</v>
       </c>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14" t="s">
+      <c r="K1" s="24"/>
+      <c r="L1" s="24" t="s">
         <v>275</v>
       </c>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14" t="s">
+      <c r="M1" s="24"/>
+      <c r="N1" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14" t="s">
+      <c r="O1" s="24"/>
+      <c r="P1" s="24" t="s">
         <v>277</v>
       </c>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14" t="s">
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="S1" s="14"/>
+      <c r="S1" s="24"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="N2" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="O2" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="P2" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="Q2" s="16" t="s">
+      <c r="Q2" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="R2" s="26" t="s">
         <v>279</v>
       </c>
-      <c r="S2" s="16" t="s">
+      <c r="S2" s="26" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="3" ht="30" spans="1:19">
-      <c r="A3" s="15"/>
-      <c r="B3" s="17" t="s">
+    <row r="3" ht="28.8" spans="1:19">
+      <c r="A3" s="25"/>
+      <c r="B3" s="27" t="s">
         <v>281</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="28" t="s">
         <v>287</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="28" t="s">
         <v>289</v>
       </c>
-      <c r="K3" s="18" t="s">
+      <c r="K3" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="28" t="s">
         <v>291</v>
       </c>
-      <c r="M3" s="18" t="s">
+      <c r="M3" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="N3" s="28" t="s">
         <v>293</v>
       </c>
-      <c r="O3" s="18" t="s">
+      <c r="O3" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="P3" s="18" t="s">
+      <c r="P3" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="Q3" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="R3" s="18" t="s">
+      <c r="R3" s="28" t="s">
         <v>297</v>
       </c>
-      <c r="S3" s="18" t="s">
+      <c r="S3" s="28" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="15"/>
-      <c r="B4" s="17" t="s">
+      <c r="A4" s="25"/>
+      <c r="B4" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="K4" s="18" t="s">
+      <c r="K4" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="L4" s="18" t="s">
+      <c r="L4" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="M4" s="18" t="s">
+      <c r="M4" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="N4" s="18" t="s">
+      <c r="N4" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="O4" s="18" t="s">
+      <c r="O4" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="P4" s="18" t="s">
+      <c r="P4" s="28" t="s">
         <v>313</v>
       </c>
-      <c r="Q4" s="18" t="s">
+      <c r="Q4" s="28" t="s">
         <v>314</v>
       </c>
-      <c r="R4" s="18" t="s">
+      <c r="R4" s="28" t="s">
         <v>315</v>
       </c>
-      <c r="S4" s="18" t="s">
+      <c r="S4" s="28" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="5" ht="30" spans="1:19">
-      <c r="A5" s="15"/>
-      <c r="B5" s="17" t="s">
+    <row r="5" ht="28.8" spans="1:19">
+      <c r="A5" s="25"/>
+      <c r="B5" s="27" t="s">
         <v>317</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="28" t="s">
         <v>320</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="28" t="s">
         <v>321</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="28" t="s">
         <v>322</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="28" t="s">
         <v>323</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="28" t="s">
         <v>324</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="28" t="s">
         <v>325</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="28" t="s">
         <v>326</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="28" t="s">
         <v>327</v>
       </c>
-      <c r="M5" s="18" t="s">
+      <c r="M5" s="28" t="s">
         <v>328</v>
       </c>
-      <c r="N5" s="18" t="s">
+      <c r="N5" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="O5" s="18" t="s">
+      <c r="O5" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="P5" s="18" t="s">
+      <c r="P5" s="28" t="s">
         <v>331</v>
       </c>
-      <c r="Q5" s="18" t="s">
+      <c r="Q5" s="28" t="s">
         <v>332</v>
       </c>
-      <c r="R5" s="18" t="s">
+      <c r="R5" s="28" t="s">
         <v>333</v>
       </c>
-      <c r="S5" s="18" t="s">
+      <c r="S5" s="28" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:19">
-      <c r="A6" s="15"/>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="27" t="s">
         <v>335</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="28" t="s">
         <v>336</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="28" t="s">
         <v>337</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="28" t="s">
         <v>338</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="28" t="s">
         <v>339</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="28" t="s">
         <v>340</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="28" t="s">
         <v>341</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="28" t="s">
         <v>342</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="18" t="s">
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="O6" s="18" t="s">
+      <c r="O6" s="28" t="s">
         <v>345</v>
       </c>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
     </row>
     <row r="7" spans="1:19">
-      <c r="A7" s="15"/>
-      <c r="B7" s="17" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="27" t="s">
         <v>346</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="28" t="s">
         <v>347</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="28" t="s">
         <v>348</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="28" t="s">
         <v>349</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="28" t="s">
         <v>350</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="28" t="s">
         <v>351</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="28" t="s">
         <v>352</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="28" t="s">
         <v>353</v>
       </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
     </row>
     <row r="8" spans="1:19">
-      <c r="A8" s="15"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="25"/>
+      <c r="B8" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="28" t="s">
         <v>355</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="28" t="s">
         <v>356</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="28" t="s">
         <v>357</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="18" t="s">
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="28" t="s">
         <v>358</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="28" t="s">
         <v>359</v>
       </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
     </row>
     <row r="9" spans="1:19">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="18" t="s">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="28" t="s">
         <v>360</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="28" t="s">
         <v>361</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
     </row>
     <row r="10" spans="1:19">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="18" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="28" t="s">
         <v>362</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="28" t="s">
         <v>363</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="18" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="28" t="s">
         <v>364</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="28" t="s">
         <v>365</v>
       </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="18" t="s">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="28" t="s">
         <v>366</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="28" t="s">
         <v>367</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5715,928 +6198,928 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H55"/>
-  <sheetFormatPr defaultColWidth="38.5714285714286" defaultRowHeight="15" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="38.5740740740741" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="15.1428571428571" style="2" customWidth="1"/>
-    <col min="2" max="2" width="38.5714285714286" style="1" customWidth="1"/>
-    <col min="3" max="3" width="26" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85714285714286" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.85714285714286" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42857142857143" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85714285714286" style="1" customWidth="1"/>
-    <col min="8" max="8" width="35.5714285714286" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="38.5714285714286" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6666666666667" style="12" customWidth="1"/>
+    <col min="2" max="2" width="38.5740740740741" style="11" customWidth="1"/>
+    <col min="3" max="3" width="26" style="11" customWidth="1"/>
+    <col min="4" max="4" width="8.86111111111111" style="11" customWidth="1"/>
+    <col min="5" max="5" width="7.86111111111111" style="11" customWidth="1"/>
+    <col min="6" max="6" width="9.42592592592593" style="11" customWidth="1"/>
+    <col min="7" max="7" width="8.86111111111111" style="11" customWidth="1"/>
+    <col min="8" max="8" width="35.5740740740741" style="11" customWidth="1"/>
+    <col min="9" max="16384" width="38.5740740740741" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="11" customFormat="1" spans="1:8">
+      <c r="A1" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="13" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="4" t="s">
+    <row r="2" s="11" customFormat="1" spans="1:8">
+      <c r="A2" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="A3" s="7"/>
-      <c r="B3" s="5" t="s">
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" s="11" customFormat="1" spans="1:8">
+      <c r="A3" s="17"/>
+      <c r="B3" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:8">
-      <c r="A4" s="7"/>
-      <c r="B4" s="5" t="s">
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+    </row>
+    <row r="4" s="11" customFormat="1" spans="1:8">
+      <c r="A4" s="17"/>
+      <c r="B4" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="15"/>
+      <c r="D4" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="A5" s="7"/>
-      <c r="B5" s="5" t="s">
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" s="11" customFormat="1" spans="1:8">
+      <c r="A5" s="17"/>
+      <c r="B5" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="A6" s="7"/>
-      <c r="B6" s="5" t="s">
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="6" s="11" customFormat="1" spans="1:8">
+      <c r="A6" s="17"/>
+      <c r="B6" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="15"/>
+      <c r="D6" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:8">
-      <c r="A7" s="7"/>
-      <c r="B7" s="5" t="s">
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+    </row>
+    <row r="7" s="11" customFormat="1" spans="1:8">
+      <c r="A7" s="17"/>
+      <c r="B7" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="15"/>
+      <c r="D7" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:8">
-      <c r="A8" s="7"/>
-      <c r="B8" s="5" t="s">
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" s="11" customFormat="1" spans="1:8">
+      <c r="A8" s="17"/>
+      <c r="B8" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="15"/>
+      <c r="D8" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:8">
-      <c r="A9" s="8" t="s">
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+    </row>
+    <row r="9" s="11" customFormat="1" spans="1:8">
+      <c r="A9" s="18" t="s">
         <v>385</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="15"/>
+      <c r="D9" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:8">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9" t="s">
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10" s="11" customFormat="1" spans="1:8">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19" t="s">
         <v>387</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="15"/>
+      <c r="D10" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:8">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9" t="s">
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" s="11" customFormat="1" spans="1:8">
+      <c r="A11" s="18"/>
+      <c r="B11" s="19" t="s">
         <v>388</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5" t="s">
+      <c r="C11" s="15"/>
+      <c r="D11" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:8">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9" t="s">
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" s="11" customFormat="1" spans="1:8">
+      <c r="A12" s="18"/>
+      <c r="B12" s="19" t="s">
         <v>389</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="15"/>
+      <c r="D12" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:8">
-      <c r="A13" s="8"/>
-      <c r="B13" s="1" t="s">
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" s="11" customFormat="1" spans="1:8">
+      <c r="A13" s="18"/>
+      <c r="B13" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="15"/>
+      <c r="D13" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:8">
-      <c r="A14" s="8"/>
-      <c r="B14" s="1" t="s">
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" s="11" customFormat="1" spans="1:8">
+      <c r="A14" s="18"/>
+      <c r="B14" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="15"/>
+      <c r="D14" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:8">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9" t="s">
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" s="11" customFormat="1" spans="1:8">
+      <c r="A15" s="18"/>
+      <c r="B15" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="15"/>
+      <c r="D15" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:8">
-      <c r="A16" s="7" t="s">
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" s="11" customFormat="1" spans="1:8">
+      <c r="A16" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="15"/>
+      <c r="D16" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:8">
-      <c r="A17" s="7"/>
-      <c r="B17" s="5" t="s">
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" s="11" customFormat="1" spans="1:8">
+      <c r="A17" s="17"/>
+      <c r="B17" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5" t="s">
+      <c r="C17" s="15"/>
+      <c r="D17" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:8">
-      <c r="A18" s="7"/>
-      <c r="B18" s="5" t="s">
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+    </row>
+    <row r="18" s="11" customFormat="1" spans="1:8">
+      <c r="A18" s="17"/>
+      <c r="B18" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5" t="s">
+      <c r="C18" s="15"/>
+      <c r="D18" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:8">
-      <c r="A19" s="7"/>
-      <c r="B19" s="5" t="s">
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+    </row>
+    <row r="19" s="11" customFormat="1" spans="1:8">
+      <c r="A19" s="17"/>
+      <c r="B19" s="15" t="s">
         <v>397</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5" t="s">
+      <c r="C19" s="15"/>
+      <c r="D19" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:8">
-      <c r="A20" s="7"/>
-      <c r="B20" s="1" t="s">
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+    </row>
+    <row r="20" s="11" customFormat="1" spans="1:8">
+      <c r="A20" s="17"/>
+      <c r="B20" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5" t="s">
+      <c r="C20" s="15"/>
+      <c r="D20" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:8">
-      <c r="A21" s="7"/>
-      <c r="B21" s="5" t="s">
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+    </row>
+    <row r="21" s="11" customFormat="1" spans="1:8">
+      <c r="A21" s="17"/>
+      <c r="B21" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5" t="s">
+      <c r="C21" s="15"/>
+      <c r="D21" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:8">
-      <c r="A22" s="7"/>
-      <c r="B22" s="5" t="s">
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+    </row>
+    <row r="22" s="11" customFormat="1" spans="1:8">
+      <c r="A22" s="17"/>
+      <c r="B22" s="15" t="s">
         <v>400</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5" t="s">
+      <c r="C22" s="15"/>
+      <c r="D22" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:8">
-      <c r="A23" s="7"/>
-      <c r="B23" s="5" t="s">
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+    </row>
+    <row r="23" s="11" customFormat="1" spans="1:8">
+      <c r="A23" s="17"/>
+      <c r="B23" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5" t="s">
+      <c r="C23" s="15"/>
+      <c r="D23" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:8">
-      <c r="A24" s="7"/>
-      <c r="B24" s="5" t="s">
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+    </row>
+    <row r="24" s="11" customFormat="1" spans="1:8">
+      <c r="A24" s="17"/>
+      <c r="B24" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5" t="s">
+      <c r="C24" s="15"/>
+      <c r="D24" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:8">
-      <c r="A25" s="7"/>
-      <c r="B25" s="5" t="s">
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+    </row>
+    <row r="25" s="11" customFormat="1" spans="1:8">
+      <c r="A25" s="17"/>
+      <c r="B25" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5" t="s">
+      <c r="C25" s="15"/>
+      <c r="D25" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:8">
-      <c r="A26" s="7"/>
-      <c r="B26" s="5" t="s">
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+    </row>
+    <row r="26" s="11" customFormat="1" spans="1:8">
+      <c r="A26" s="17"/>
+      <c r="B26" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5" t="s">
+      <c r="C26" s="15"/>
+      <c r="D26" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:8">
-      <c r="A27" s="4" t="s">
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+    </row>
+    <row r="27" s="11" customFormat="1" spans="1:8">
+      <c r="A27" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5" t="s">
+      <c r="C27" s="15"/>
+      <c r="D27" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:8">
-      <c r="A28" s="7"/>
-      <c r="B28" s="5" t="s">
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+    </row>
+    <row r="28" s="11" customFormat="1" spans="1:8">
+      <c r="A28" s="17"/>
+      <c r="B28" s="15" t="s">
         <v>406</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5" t="s">
+      <c r="C28" s="15"/>
+      <c r="D28" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:8">
-      <c r="A29" s="7"/>
-      <c r="B29" s="5" t="s">
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+    </row>
+    <row r="29" s="11" customFormat="1" spans="1:8">
+      <c r="A29" s="17"/>
+      <c r="B29" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5" t="s">
+      <c r="C29" s="15"/>
+      <c r="D29" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:8">
-      <c r="A30" s="7"/>
-      <c r="B30" s="5" t="s">
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+    </row>
+    <row r="30" s="11" customFormat="1" spans="1:8">
+      <c r="A30" s="17"/>
+      <c r="B30" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5" t="s">
+      <c r="C30" s="15"/>
+      <c r="D30" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:8">
-      <c r="A31" s="7" t="s">
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+    </row>
+    <row r="31" s="11" customFormat="1" spans="1:8">
+      <c r="A31" s="17" t="s">
         <v>409</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5" t="s">
+      <c r="C31" s="15"/>
+      <c r="D31" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:8">
-      <c r="A32" s="7"/>
-      <c r="B32" s="5" t="s">
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+    </row>
+    <row r="32" s="11" customFormat="1" spans="1:8">
+      <c r="A32" s="17"/>
+      <c r="B32" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5" t="s">
+      <c r="C32" s="15"/>
+      <c r="D32" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:8">
-      <c r="A33" s="7"/>
-      <c r="B33" s="5" t="s">
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+    </row>
+    <row r="33" s="11" customFormat="1" spans="1:8">
+      <c r="A33" s="17"/>
+      <c r="B33" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5" t="s">
+      <c r="C33" s="15"/>
+      <c r="D33" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:8">
-      <c r="A34" s="7"/>
-      <c r="B34" s="5" t="s">
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+    </row>
+    <row r="34" s="11" customFormat="1" spans="1:8">
+      <c r="A34" s="17"/>
+      <c r="B34" s="15" t="s">
         <v>413</v>
       </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5" t="s">
+      <c r="C34" s="15"/>
+      <c r="D34" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:8">
-      <c r="A35" s="7" t="s">
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+    </row>
+    <row r="35" s="11" customFormat="1" spans="1:8">
+      <c r="A35" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="15" t="s">
         <v>415</v>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5" t="s">
+      <c r="C35" s="15"/>
+      <c r="D35" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:8">
-      <c r="A36" s="7"/>
-      <c r="B36" s="5" t="s">
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+    </row>
+    <row r="36" s="11" customFormat="1" spans="1:8">
+      <c r="A36" s="17"/>
+      <c r="B36" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5" t="s">
+      <c r="C36" s="15"/>
+      <c r="D36" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:8">
-      <c r="A37" s="7"/>
-      <c r="B37" s="5" t="s">
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+    </row>
+    <row r="37" s="11" customFormat="1" spans="1:8">
+      <c r="A37" s="17"/>
+      <c r="B37" s="15" t="s">
         <v>417</v>
       </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="15"/>
+      <c r="D37" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:8">
-      <c r="A38" s="7"/>
-      <c r="B38" s="5" t="s">
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+    </row>
+    <row r="38" s="11" customFormat="1" spans="1:8">
+      <c r="A38" s="17"/>
+      <c r="B38" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5" t="s">
+      <c r="C38" s="15"/>
+      <c r="D38" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:8">
-      <c r="A39" s="7"/>
-      <c r="B39" s="5" t="s">
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+    </row>
+    <row r="39" s="11" customFormat="1" spans="1:8">
+      <c r="A39" s="17"/>
+      <c r="B39" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5" t="s">
+      <c r="C39" s="15"/>
+      <c r="D39" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:8">
-      <c r="A40" s="10"/>
-      <c r="B40" s="5" t="s">
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+    </row>
+    <row r="40" s="11" customFormat="1" spans="1:8">
+      <c r="A40" s="20"/>
+      <c r="B40" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5" t="s">
+      <c r="C40" s="15"/>
+      <c r="D40" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:8">
-      <c r="A41" s="7" t="s">
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+    </row>
+    <row r="41" s="11" customFormat="1" spans="1:8">
+      <c r="A41" s="17" t="s">
         <v>421</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="15" t="s">
         <v>422</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5" t="s">
+      <c r="C41" s="15"/>
+      <c r="D41" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:8">
-      <c r="A42" s="7"/>
-      <c r="B42" s="5" t="s">
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+    </row>
+    <row r="42" s="11" customFormat="1" spans="1:8">
+      <c r="A42" s="17"/>
+      <c r="B42" s="15" t="s">
         <v>423</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5" t="s">
+      <c r="C42" s="15"/>
+      <c r="D42" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:8">
-      <c r="A43" s="11"/>
-      <c r="B43" s="5" t="s">
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+    </row>
+    <row r="43" s="11" customFormat="1" spans="1:8">
+      <c r="A43" s="21"/>
+      <c r="B43" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5" t="s">
+      <c r="C43" s="15"/>
+      <c r="D43" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="1:8">
-      <c r="A44" s="12" t="s">
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+    </row>
+    <row r="44" s="11" customFormat="1" spans="1:8">
+      <c r="A44" s="22" t="s">
         <v>425</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="15" t="s">
         <v>426</v>
       </c>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5" t="s">
+      <c r="C44" s="15"/>
+      <c r="D44" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="1:8">
-      <c r="A45" s="12"/>
-      <c r="B45" s="5" t="s">
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+    </row>
+    <row r="45" s="11" customFormat="1" spans="1:8">
+      <c r="A45" s="22"/>
+      <c r="B45" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5" t="s">
+      <c r="C45" s="15"/>
+      <c r="D45" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-    </row>
-    <row r="46" s="1" customFormat="1" spans="1:8">
-      <c r="A46" s="12"/>
-      <c r="B46" s="5" t="s">
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+    </row>
+    <row r="46" s="11" customFormat="1" spans="1:8">
+      <c r="A46" s="22"/>
+      <c r="B46" s="15" t="s">
         <v>428</v>
       </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5" t="s">
+      <c r="C46" s="15"/>
+      <c r="D46" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-    </row>
-    <row r="47" s="1" customFormat="1" spans="1:8">
-      <c r="A47" s="12"/>
-      <c r="B47" s="5" t="s">
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+    </row>
+    <row r="47" s="11" customFormat="1" spans="1:8">
+      <c r="A47" s="22"/>
+      <c r="B47" s="15" t="s">
         <v>428</v>
       </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5" t="s">
+      <c r="C47" s="15"/>
+      <c r="D47" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-    </row>
-    <row r="48" s="1" customFormat="1" spans="1:8">
-      <c r="A48" s="12" t="s">
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+    </row>
+    <row r="48" s="11" customFormat="1" spans="1:8">
+      <c r="A48" s="22" t="s">
         <v>429</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5" t="s">
+      <c r="C48" s="15"/>
+      <c r="D48" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-    </row>
-    <row r="49" s="1" customFormat="1" spans="1:8">
-      <c r="A49" s="12"/>
-      <c r="B49" s="5" t="s">
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+    </row>
+    <row r="49" s="11" customFormat="1" spans="1:8">
+      <c r="A49" s="22"/>
+      <c r="B49" s="15" t="s">
         <v>431</v>
       </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5" t="s">
+      <c r="C49" s="15"/>
+      <c r="D49" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-    </row>
-    <row r="50" s="1" customFormat="1" spans="1:8">
-      <c r="A50" s="12"/>
-      <c r="B50" s="5" t="s">
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+    </row>
+    <row r="50" s="11" customFormat="1" spans="1:8">
+      <c r="A50" s="22"/>
+      <c r="B50" s="15" t="s">
         <v>432</v>
       </c>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5" t="s">
+      <c r="C50" s="15"/>
+      <c r="D50" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
-    </row>
-    <row r="51" s="1" customFormat="1" spans="1:8">
-      <c r="A51" s="12"/>
-      <c r="B51" s="5" t="s">
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+    </row>
+    <row r="51" s="11" customFormat="1" spans="1:8">
+      <c r="A51" s="22"/>
+      <c r="B51" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5" t="s">
+      <c r="C51" s="15"/>
+      <c r="D51" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-    </row>
-    <row r="52" s="1" customFormat="1" spans="1:8">
-      <c r="A52" s="12" t="s">
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+    </row>
+    <row r="52" s="11" customFormat="1" spans="1:8">
+      <c r="A52" s="22" t="s">
         <v>434</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5" t="s">
+      <c r="C52" s="15"/>
+      <c r="D52" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="1:8">
-      <c r="A53" s="12"/>
-      <c r="B53" s="5" t="s">
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+    </row>
+    <row r="53" s="11" customFormat="1" spans="1:8">
+      <c r="A53" s="22"/>
+      <c r="B53" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5" t="s">
+      <c r="C53" s="15"/>
+      <c r="D53" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-    </row>
-    <row r="54" s="1" customFormat="1" spans="1:8">
-      <c r="A54" s="12"/>
-      <c r="B54" s="5" t="s">
+      <c r="F53" s="15"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15"/>
+    </row>
+    <row r="54" s="11" customFormat="1" spans="1:8">
+      <c r="A54" s="22"/>
+      <c r="B54" s="15" t="s">
         <v>437</v>
       </c>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5" t="s">
+      <c r="C54" s="15"/>
+      <c r="D54" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-    </row>
-    <row r="55" s="1" customFormat="1" spans="1:8">
-      <c r="A55" s="12"/>
-      <c r="B55" s="5" t="s">
+      <c r="F54" s="15"/>
+      <c r="G54" s="15"/>
+      <c r="H54" s="15"/>
+    </row>
+    <row r="55" s="11" customFormat="1" spans="1:8">
+      <c r="A55" s="22"/>
+      <c r="B55" s="15" t="s">
         <v>438</v>
       </c>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5" t="s">
+      <c r="C55" s="15"/>
+      <c r="D55" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="16" t="s">
         <v>381</v>
       </c>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6652,7 +7135,7 @@
     <mergeCell ref="A52:A55"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D2:D55">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D55">
       <formula1>"PENDING,IN-Work,COMPLETED"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E$1:E$1048576">
@@ -6662,4 +7145,297 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="21.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="36.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="21.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2"/>
+      <c r="B20" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2"/>
+      <c r="B21" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2"/>
+      <c r="B22" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2"/>
+      <c r="B23" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2"/>
+      <c r="B24" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="9"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="9"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="10"/>
+      <c r="B28" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A17:A24"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="C22:C24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>